--- a/exports/SBILIFE_full_report.xlsx
+++ b/exports/SBILIFE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>3.87</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1245</v>
+        <v>1235.8</v>
       </c>
       <c r="I2" t="n">
         <v>1239.381628714845</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.14</v>
+        <v>0.39</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>4.84</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44622.38541666666</v>
+        <v>44622.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1105.45</v>
+        <v>1120.05</v>
       </c>
       <c r="I3" t="n">
         <v>1113.433235720759</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>10.55</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>2.15</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>7.8</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44624.55208333334</v>
+        <v>44627.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1056.5</v>
+        <v>1030</v>
       </c>
       <c r="I4" t="n">
         <v>1032.637746159566</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.67</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>6.28</v>
+        <v>8.6</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>2.83</v>
       </c>
       <c r="N4" t="n">
         <v>3.22</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1084</v>
+        <v>1117.45</v>
       </c>
       <c r="I5" t="n">
         <v>1092.915377351392</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.24</v>
+        <v>-8.49</v>
       </c>
       <c r="L5" t="n">
-        <v>6.58</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>1.77</v>
+        <v>3.69</v>
       </c>
       <c r="O5" t="n">
         <v>-2.7</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>7.2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1134.15</v>
+        <v>1100.8</v>
       </c>
       <c r="I6" t="n">
         <v>1107.242131961688</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K6" t="n">
-        <v>1.49</v>
+        <v>-1.49</v>
       </c>
       <c r="L6" t="n">
         <v>5.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.74</v>
+        <v>1.25</v>
       </c>
       <c r="N6" t="n">
         <v>3.97</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.98</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44707.55208333334</v>
+        <v>44708.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1106.6</v>
+        <v>1122.55</v>
       </c>
       <c r="I7" t="n">
         <v>1115.55404202855</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.53</v>
+        <v>-1.98</v>
       </c>
       <c r="L7" t="n">
         <v>2.89</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1124.1</v>
+        <v>1108.5</v>
       </c>
       <c r="I8" t="n">
         <v>1108.676993683924</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>0.14</v>
+        <v>-1.25</v>
       </c>
       <c r="L8" t="n">
         <v>1.57</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.17</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44746.55208333334</v>
+        <v>44747.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1116.35</v>
+        <v>1124.95</v>
       </c>
       <c r="I9" t="n">
         <v>1122.328455732887</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.71</v>
+        <v>-1.48</v>
       </c>
       <c r="L9" t="n">
         <v>2.63</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>1266.1</v>
+        <v>1259.25</v>
       </c>
       <c r="I10" t="n">
         <v>1265.242896002193</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>83</v>
+        <v>83.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>12.55</v>
+        <v>11.94</v>
       </c>
       <c r="L10" t="n">
         <v>1.5</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.82</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44854.55208333334</v>
+        <v>44855.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1226.3</v>
+        <v>1241.55</v>
       </c>
       <c r="I11" t="n">
         <v>1241.204252599482</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>2.62</v>
+        <v>1.41</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>4.91</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1243.25</v>
+        <v>1219.9</v>
       </c>
       <c r="I12" t="n">
         <v>1228.797547063814</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K12" t="n">
-        <v>0.14</v>
+        <v>-1.74</v>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
         <v>1.79</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>5.04</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44893.55208333334</v>
+        <v>44894.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1258</v>
+        <v>1271.05</v>
       </c>
       <c r="I13" t="n">
         <v>1270.654146118777</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.12</v>
+        <v>-4.19</v>
       </c>
       <c r="L13" t="n">
-        <v>4.07</v>
+        <v>4.38</v>
       </c>
       <c r="M13" t="n">
         <v>0.5</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>5.1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44915.38541666666</v>
+        <v>44915.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1243.55</v>
+        <v>1229.4</v>
       </c>
       <c r="I14" t="n">
         <v>1236.205633070055</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.16</v>
+        <v>-3.28</v>
       </c>
       <c r="L14" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.35</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>4.92</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44931.55208333334</v>
+        <v>44932.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1272</v>
+        <v>1282.35</v>
       </c>
       <c r="I15" t="n">
         <v>1273.436394075208</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.47</v>
+        <v>-4.31</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3</v>
+        <v>4.68</v>
       </c>
       <c r="M15" t="n">
         <v>0.6</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.7</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44950.38541666666</v>
+        <v>44950.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>1278.4</v>
+        <v>1272.65</v>
       </c>
       <c r="I16" t="n">
         <v>1275.122823869307</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.31</v>
+        <v>-0.76</v>
       </c>
       <c r="L16" t="n">
         <v>1.24</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.4</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45007.55208333334</v>
+        <v>45008.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1111.05</v>
+        <v>1124.5</v>
       </c>
       <c r="I17" t="n">
         <v>1119.796429708719</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K17" t="n">
-        <v>12.7</v>
+        <v>11.64</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.04</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1108.5</v>
+        <v>1098.45</v>
       </c>
       <c r="I18" t="n">
         <v>1105.164140715753</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.42</v>
+        <v>-2.32</v>
       </c>
       <c r="L18" t="n">
         <v>3.67</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.38</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1140</v>
+        <v>1149.85</v>
       </c>
       <c r="I19" t="n">
         <v>1146.564072699491</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.78</v>
+        <v>-4.68</v>
       </c>
       <c r="L19" t="n">
-        <v>4.51</v>
+        <v>5.42</v>
       </c>
       <c r="M19" t="n">
         <v>1.58</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.77</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1161.25</v>
+        <v>1154.5</v>
       </c>
       <c r="I20" t="n">
         <v>1156.079739383175</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K20" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.35</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.42</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45071.55208333334</v>
+        <v>45072.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1181.8</v>
+        <v>1194.65</v>
       </c>
       <c r="I21" t="n">
         <v>1189.966509005753</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.36</v>
+        <v>-3.48</v>
       </c>
       <c r="L21" t="n">
-        <v>2.38</v>
+        <v>3.51</v>
       </c>
       <c r="M21" t="n">
         <v>0.26</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.05</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1277.4</v>
+        <v>1268.7</v>
       </c>
       <c r="I22" t="n">
         <v>1271.105115606863</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K22" t="n">
-        <v>6.93</v>
+        <v>6.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.8</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.47</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45145.55208333334</v>
+        <v>45146.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1305</v>
+        <v>1341.8</v>
       </c>
       <c r="I23" t="n">
         <v>1306.234532248502</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.86</v>
+        <v>-5.76</v>
       </c>
       <c r="L23" t="n">
-        <v>2.92</v>
+        <v>6.13</v>
       </c>
       <c r="M23" t="n">
         <v>0.63</v>
       </c>
       <c r="N23" t="n">
-        <v>3.16</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>-1.52</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>6.72</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45154.55208333334</v>
+        <v>45155.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1290</v>
+        <v>1277.6</v>
       </c>
       <c r="I24" t="n">
         <v>1288.269602377592</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.86</v>
+        <v>-4.78</v>
       </c>
       <c r="L24" t="n">
-        <v>4.53</v>
+        <v>4.89</v>
       </c>
       <c r="M24" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="N24" t="n">
         <v>1.98</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.71</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45173.38541666666</v>
+        <v>45173.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1315.3</v>
+        <v>1332</v>
       </c>
       <c r="I25" t="n">
         <v>1327.60923000391</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.95</v>
+        <v>-4.26</v>
       </c>
       <c r="L25" t="n">
-        <v>3.98</v>
+        <v>4.29</v>
       </c>
       <c r="M25" t="n">
         <v>0.93</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>4.34</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45190.55208333334</v>
+        <v>45191.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1341.95</v>
+        <v>1330</v>
       </c>
       <c r="I26" t="n">
         <v>1331.057749814741</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="L26" t="n">
         <v>1.99</v>
       </c>
       <c r="M26" t="n">
-        <v>0.32</v>
+        <v>1.18</v>
       </c>
       <c r="N26" t="n">
         <v>1.96</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>3.77</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45212.55208333334</v>
+        <v>45215.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1318.25</v>
+        <v>1328.25</v>
       </c>
       <c r="I27" t="n">
         <v>1322.463116677877</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K27" t="n">
-        <v>0.88</v>
+        <v>0.13</v>
       </c>
       <c r="L27" t="n">
         <v>0.75</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.08</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45224.38541666666</v>
+        <v>45224.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1315.15</v>
+        <v>1311</v>
       </c>
       <c r="I28" t="n">
         <v>1315.053892355728</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.99</v>
+        <v>-1.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>0.9</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>4.29</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45229.55208333334</v>
+        <v>45230.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1325.5</v>
+        <v>1361.9</v>
       </c>
       <c r="I29" t="n">
         <v>1351.956730058739</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.11</v>
+        <v>-3.88</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="M29" t="n">
         <v>0.37</v>
       </c>
       <c r="N29" t="n">
-        <v>1.42</v>
+        <v>3.36</v>
       </c>
       <c r="O29" t="n">
         <v>-1.8</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.78</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45279.55208333334</v>
+        <v>45280.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1428.5</v>
+        <v>1417.75</v>
       </c>
       <c r="I30" t="n">
         <v>1425.943784267149</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K30" t="n">
-        <v>4.89</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
         <v>3.11</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.42</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45296.38541666666</v>
+        <v>45296.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1447.25</v>
+        <v>1454.5</v>
       </c>
       <c r="I31" t="n">
         <v>1448.947910579523</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.08</v>
+        <v>-2.59</v>
       </c>
       <c r="L31" t="n">
         <v>3.54</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>3.77</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1443.65</v>
+        <v>1375.55</v>
       </c>
       <c r="I32" t="n">
         <v>1402.576031075935</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.75</v>
+        <v>-5.43</v>
       </c>
       <c r="L32" t="n">
-        <v>4.83</v>
+        <v>5.78</v>
       </c>
       <c r="M32" t="n">
         <v>0.85</v>
       </c>
       <c r="N32" t="n">
-        <v>2.62</v>
+        <v>4.76</v>
       </c>
       <c r="O32" t="n">
         <v>1.69</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.68</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45328.38541666666</v>
+        <v>45328.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1435.7</v>
+        <v>1468.85</v>
       </c>
       <c r="I33" t="n">
         <v>1458.227679579329</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.37</v>
+        <v>-6.78</v>
       </c>
       <c r="L33" t="n">
-        <v>6.14</v>
+        <v>6.86</v>
       </c>
       <c r="M33" t="n">
         <v>1.53</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.52</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45366.55208333334</v>
+        <v>45369.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1502.35</v>
+        <v>1483.8</v>
       </c>
       <c r="I34" t="n">
         <v>1485.206142898138</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="L34" t="n">
         <v>3.1</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.17</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1427</v>
+        <v>1447</v>
       </c>
       <c r="I35" t="n">
         <v>1445.318401595239</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>81.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K35" t="n">
-        <v>3.83</v>
+        <v>2.48</v>
       </c>
       <c r="L35" t="n">
         <v>2.98</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.75</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45520.55208333334</v>
+        <v>45523.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1690.9</v>
+        <v>1668.7</v>
       </c>
       <c r="I36" t="n">
         <v>1679.054120698066</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K36" t="n">
-        <v>16.86</v>
+        <v>15.32</v>
       </c>
       <c r="L36" t="n">
         <v>1.98</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>5.82</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45524.38541666666</v>
+        <v>45524.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1732.4</v>
+        <v>1763.2</v>
       </c>
       <c r="I37" t="n">
         <v>1750.783507223713</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.82</v>
+        <v>-5.66</v>
       </c>
       <c r="L37" t="n">
-        <v>3.82</v>
+        <v>6.12</v>
       </c>
       <c r="M37" t="n">
         <v>0.35</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.89</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1845</v>
+        <v>1819.35</v>
       </c>
       <c r="I38" t="n">
         <v>1839.890393571739</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>4.64</v>
+        <v>3.18</v>
       </c>
       <c r="L38" t="n">
         <v>1.78</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.86</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1872.55</v>
+        <v>1900.55</v>
       </c>
       <c r="I39" t="n">
         <v>1895.466645614105</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.92</v>
+        <v>-4.46</v>
       </c>
       <c r="L39" t="n">
-        <v>3.61</v>
+        <v>4.64</v>
       </c>
       <c r="M39" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="N39" t="n">
-        <v>1.43</v>
+        <v>2.53</v>
       </c>
       <c r="O39" t="n">
         <v>-1.19</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>4.61</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1845</v>
+        <v>1829.7</v>
       </c>
       <c r="I40" t="n">
         <v>1834.294911546688</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.92</v>
+        <v>-3.73</v>
       </c>
       <c r="L40" t="n">
-        <v>3.28</v>
+        <v>4.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="N40" t="n">
         <v>2.78</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.54</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1418.35</v>
+        <v>1448.15</v>
       </c>
       <c r="I41" t="n">
         <v>1445.79955277441</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>93.16666666666667</v>
+        <v>94</v>
       </c>
       <c r="K41" t="n">
-        <v>22.48</v>
+        <v>20.85</v>
       </c>
       <c r="L41" t="n">
         <v>1.62</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>4.66</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45680.38541666666</v>
+        <v>45680.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>1457.8</v>
+        <v>1451.3</v>
       </c>
       <c r="I42" t="n">
         <v>1452.869933064593</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="L42" t="n">
         <v>1.61</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>5.18</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45733.55208333334</v>
+        <v>45734.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1439.5</v>
+        <v>1452</v>
       </c>
       <c r="I43" t="n">
         <v>1442.907188854444</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>53</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="L43" t="n">
         <v>5.28</v>
       </c>
       <c r="M43" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="N43" t="n">
         <v>3.56</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>4.99</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1512.05</v>
+        <v>1449.6</v>
       </c>
       <c r="I44" t="n">
         <v>1505.333534659675</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>4.14</v>
+        <v>-0.17</v>
       </c>
       <c r="L44" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M44" t="n">
-        <v>0.79</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.01</v>
+        <v>2.91</v>
       </c>
       <c r="O44" t="n">
         <v>1.27</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.22</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1526</v>
+        <v>1569.2</v>
       </c>
       <c r="I45" t="n">
         <v>1539.563801156355</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.27</v>
+        <v>-8.25</v>
       </c>
       <c r="L45" t="n">
-        <v>6.17</v>
+        <v>8.31</v>
       </c>
       <c r="M45" t="n">
         <v>3.8</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.95</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45811.55208333334</v>
+        <v>45812.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1779.4</v>
+        <v>1769.8</v>
       </c>
       <c r="I46" t="n">
         <v>1771.361483533103</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K46" t="n">
-        <v>13.4</v>
+        <v>12.78</v>
       </c>
       <c r="L46" t="n">
         <v>2.82</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>3.23</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45827.55208333334</v>
+        <v>45828.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1790</v>
+        <v>1814.5</v>
       </c>
       <c r="I47" t="n">
         <v>1807.400929124218</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.14</v>
+        <v>-2.53</v>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="M47" t="n">
         <v>0.67</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.47</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45841.55208333334</v>
+        <v>45842.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1804</v>
+        <v>1786.5</v>
       </c>
       <c r="I48" t="n">
         <v>1803.524755270077</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.58</v>
+        <v>-1.54</v>
       </c>
       <c r="L48" t="n">
         <v>1.95</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>4.6</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1836.2</v>
+        <v>1845.9</v>
       </c>
       <c r="I49" t="n">
         <v>1845.234157400508</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.78</v>
+        <v>-3.32</v>
       </c>
       <c r="L49" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
         <v>0.5600000000000001</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.32</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45898.38541666666</v>
+        <v>45898.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1814</v>
+        <v>1806.8</v>
       </c>
       <c r="I50" t="n">
         <v>1808.385019520564</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.73</v>
+        <v>-2.12</v>
       </c>
       <c r="L50" t="n">
         <v>3.52</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>3.83</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1845</v>
+        <v>1867</v>
       </c>
       <c r="I51" t="n">
         <v>1860.34752183023</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.11</v>
+        <v>-3.33</v>
       </c>
       <c r="L51" t="n">
         <v>4.6</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>3.52</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1812.4</v>
+        <v>1794.6</v>
       </c>
       <c r="I52" t="n">
         <v>1801.350062564406</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.92</v>
+        <v>-3.88</v>
       </c>
       <c r="L52" t="n">
-        <v>3.72</v>
+        <v>3.96</v>
       </c>
       <c r="M52" t="n">
         <v>0.52</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.16</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1815</v>
+        <v>1845.3</v>
       </c>
       <c r="I53" t="n">
         <v>1830.842595386143</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.14</v>
+        <v>-2.83</v>
       </c>
       <c r="L53" t="n">
-        <v>2.74</v>
+        <v>3.56</v>
       </c>
       <c r="M53" t="n">
         <v>0.6899999999999999</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.15</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>2001.8</v>
+        <v>1972.2</v>
       </c>
       <c r="I54" t="n">
         <v>1976.043183551586</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K54" t="n">
-        <v>8.48</v>
+        <v>6.88</v>
       </c>
       <c r="L54" t="n">
         <v>1.94</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.13</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45995.55208333334</v>
+        <v>45996.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2000.7</v>
+        <v>2042.6</v>
       </c>
       <c r="I55" t="n">
         <v>2040.964210662128</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.45</v>
+        <v>-3.57</v>
       </c>
       <c r="L55" t="n">
-        <v>1.97</v>
+        <v>3.58</v>
       </c>
       <c r="M55" t="n">
         <v>0.46</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.02</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2009.6</v>
+        <v>1973.6</v>
       </c>
       <c r="I56" t="n">
         <v>1975.519359217914</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.62</v>
+        <v>-3.38</v>
       </c>
       <c r="L56" t="n">
-        <v>2.56</v>
+        <v>3.51</v>
       </c>
       <c r="M56" t="n">
         <v>0.68</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>3.76</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>2044</v>
+        <v>2067.6</v>
       </c>
       <c r="I57" t="n">
         <v>2047.873178075414</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.57</v>
+        <v>-4.76</v>
       </c>
       <c r="L57" t="n">
-        <v>3.66</v>
+        <v>5.25</v>
       </c>
       <c r="M57" t="n">
         <v>0.04</v>
       </c>
       <c r="N57" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="O57" t="n">
         <v>0.5</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>3.88</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46043.55208333334</v>
+        <v>46044.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2050.1</v>
+        <v>2025</v>
       </c>
       <c r="I58" t="n">
         <v>2035.081594057127</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.85</v>
+        <v>-2.06</v>
       </c>
       <c r="L58" t="n">
-        <v>1.42</v>
+        <v>2.76</v>
       </c>
       <c r="M58" t="n">
         <v>0.76</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>4.4</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46073.55208333334</v>
+        <v>46076.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>2081.1</v>
+        <v>2111</v>
       </c>
       <c r="I59" t="n">
         <v>2087.768181943397</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.77</v>
+        <v>-4.25</v>
       </c>
       <c r="L59" t="n">
-        <v>2.88</v>
+        <v>5.28</v>
       </c>
       <c r="M59" t="n">
         <v>2.68</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>4.13</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>2038.5</v>
+        <v>1999.8</v>
       </c>
       <c r="I60" t="n">
         <v>2032.512576642066</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.43</v>
+        <v>-5.27</v>
       </c>
       <c r="L60" t="n">
-        <v>3.79</v>
+        <v>5.42</v>
       </c>
       <c r="M60" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="N60" t="n">
         <v>2.23</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1838.1</v>
+        <v>1919.4</v>
       </c>
       <c r="I61" t="n">
         <v>1869.108315618455</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K61" t="n">
-        <v>8.09</v>
+        <v>4.02</v>
       </c>
       <c r="L61" t="n">
         <v>2.68</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.72</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46133.55208333334</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1914</v>
+        <v>1891</v>
       </c>
       <c r="I62" t="n">
         <v>1899.047844221134</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.28</v>
+        <v>-1.48</v>
       </c>
       <c r="L62" t="n">
         <v>2.57</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.01</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46150.55208333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1871.1</v>
+        <v>1886.6</v>
       </c>
       <c r="I63" t="n">
         <v>1878.346949469114</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K63" t="n">
-        <v>1.05</v>
+        <v>0.23</v>
       </c>
       <c r="L63" t="n">
         <v>2.09</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>4.39</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1839</v>
+        <v>1824.6</v>
       </c>
       <c r="I64" t="n">
         <v>1825.466084165955</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.52</v>
+        <v>-3.29</v>
       </c>
       <c r="L64" t="n">
-        <v>3.63</v>
+        <v>4.43</v>
       </c>
       <c r="M64" t="n">
         <v>1.47</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.17</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>1778.7</v>
+        <v>1801.9</v>
       </c>
       <c r="I65" t="n">
         <v>1786.437186822171</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>2.52</v>
+        <v>1.24</v>
       </c>
       <c r="L65" t="n">
         <v>1.19</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.1</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46244.55208333334</v>
+        <v>46245.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1850.4</v>
+        <v>1816.6</v>
       </c>
       <c r="I66" t="n">
         <v>1840.437621021056</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>54</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>2.69</v>
+        <v>0.82</v>
       </c>
       <c r="L66" t="n">
         <v>3.61</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.56</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46281.55208333334</v>
+        <v>46282.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1700.3</v>
+        <v>1764.7</v>
       </c>
       <c r="I67" t="n">
         <v>1723.359387929427</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K67" t="n">
-        <v>6.4</v>
+        <v>2.86</v>
       </c>
       <c r="L67" t="n">
         <v>2.72</v>
@@ -4260,7 +5063,7 @@
         <v>0.84</v>
       </c>
       <c r="N67" t="n">
-        <v>3.21</v>
+        <v>4.04</v>
       </c>
       <c r="O67" t="n">
         <v>-0.9</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.96</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46295.38541666666</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>1701.5</v>
+        <v>1684.7</v>
       </c>
       <c r="I68" t="n">
         <v>1691.674342847333</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.58</v>
+        <v>-4.53</v>
       </c>
       <c r="L68" t="n">
-        <v>4.29</v>
+        <v>4.74</v>
       </c>
       <c r="M68" t="n">
         <v>2.69</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>35</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>93.2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.6</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.4</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7372,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7382,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7392,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>73.09999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.88</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.37</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.38</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.48</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.8</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.96</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.58</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="25">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="27">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
